--- a/survey_templates/046_mardi_gras_royalty_voting--survey_templates.xlsx
+++ b/survey_templates/046_mardi_gras_royalty_voting--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -707,7 +707,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C22"/>
+  <dimension ref="A1:C20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="29" customWidth="1" min="1" max="1"/>
@@ -757,29 +757,29 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>king_krew</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>King Krew</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>krewes_choices</t>
+          <t>event_committees_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>king_krew</t>
+          <t>mardi_gras_committee</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>King Krew</t>
+          <t>Mardi Gras Committee</t>
         </is>
       </c>
     </row>
@@ -791,46 +791,46 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>mardi_gras_committee</t>
+          <t>event_committee</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Mardi Gras Committee</t>
+          <t>Event Committee</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>event_committees_choices</t>
+          <t>candidates_for_king_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>event_committee</t>
+          <t>candidate_1</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Event Committee</t>
+          <t>Candidate 1</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>event_committees_choices</t>
+          <t>candidates_for_king_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>mardi_gras_committee</t>
+          <t>candidate_2</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Mardi Gras Committee</t>
+          <t>Candidate 2</t>
         </is>
       </c>
     </row>
@@ -842,46 +842,46 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>candidate_1</t>
+          <t>candidate_3</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Candidate 1</t>
+          <t>Candidate 3</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>candidates_for_king_choices</t>
+          <t>vote_for_king_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>candidate_2</t>
+          <t>1._candidate_1</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Candidate 2</t>
+          <t>1. Candidate 1</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>candidates_for_king_choices</t>
+          <t>vote_for_king_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>candidate_3</t>
+          <t>2._candidate_2</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Candidate 3</t>
+          <t>2. Candidate 2</t>
         </is>
       </c>
     </row>
@@ -893,46 +893,46 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>1._candidate_1</t>
+          <t>3._candidate_3</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>1. Candidate 1</t>
+          <t>3. Candidate 3</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>vote_for_king_choices</t>
+          <t>vote_for_queen_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2._candidate_2</t>
+          <t>1._candidate_1</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2. Candidate 2</t>
+          <t>1. Candidate 1</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>vote_for_king_choices</t>
+          <t>vote_for_queen_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>3._candidate_3</t>
+          <t>2._candidate_2</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>3. Candidate 3</t>
+          <t>2. Candidate 2</t>
         </is>
       </c>
     </row>
@@ -944,46 +944,46 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>1._candidate_1</t>
+          <t>3._candidate_3</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>1. Candidate 1</t>
+          <t>3. Candidate 3</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>vote_for_queen_choices</t>
+          <t>vote_for_duke_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2._candidate_2</t>
+          <t>1._candidate_1</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2. Candidate 2</t>
+          <t>1. Candidate 1</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>vote_for_queen_choices</t>
+          <t>vote_for_duke_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>3._candidate_3</t>
+          <t>2._candidate_2</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>3. Candidate 3</t>
+          <t>2. Candidate 2</t>
         </is>
       </c>
     </row>
@@ -995,46 +995,46 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>1._candidate_1</t>
+          <t>3._candidate_3</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>1. Candidate 1</t>
+          <t>3. Candidate 3</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>vote_for_duke_choices</t>
+          <t>vote_for_duchess_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2._candidate_2</t>
+          <t>1._candidate_1</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2. Candidate 2</t>
+          <t>1. Candidate 1</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>vote_for_duke_choices</t>
+          <t>vote_for_duchess_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>3._candidate_3</t>
+          <t>2._candidate_2</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>3. Candidate 3</t>
+          <t>2. Candidate 2</t>
         </is>
       </c>
     </row>
@@ -1046,44 +1046,10 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>1._candidate_1</t>
+          <t>3._candidate_3</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
-        <is>
-          <t>1. Candidate 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>vote_for_duchess_choices</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>2._candidate_2</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>2. Candidate 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>vote_for_duchess_choices</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>3._candidate_3</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
         <is>
           <t>3. Candidate 3</t>
         </is>
